--- a/tests/output_table_rt.xlsx
+++ b/tests/output_table_rt.xlsx
@@ -16,22 +16,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>venta</t>
+  </si>
+  <si>
+    <t>precio</t>
+  </si>
+  <si>
     <t>activo</t>
   </si>
   <si>
     <t>meta</t>
-  </si>
-  <si>
-    <t>nombre</t>
-  </si>
-  <si>
-    <t>precio</t>
-  </si>
-  <si>
-    <t>region</t>
-  </si>
-  <si>
-    <t>venta</t>
   </si>
   <si>
     <t>ana</t>
@@ -429,123 +429,123 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" t="b">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>150</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" t="s">
         <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
       </c>
       <c r="D2">
         <v>1.5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="b">
-        <v>0</v>
-      </c>
-      <c r="B3">
-        <v>150</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
+      <c r="C3">
+        <v>200</v>
       </c>
       <c r="D3">
         <v>2.5</v>
       </c>
-      <c r="E3" t="s">
-        <v>7</v>
+      <c r="E3" t="b">
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" t="b">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>250</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="A4" t="s">
         <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>300</v>
       </c>
       <c r="D4">
         <v>3.5</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="F4">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="b">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>500</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
+      <c r="C5">
+        <v>400</v>
       </c>
       <c r="D5">
         <v>4.5</v>
       </c>
-      <c r="E5" t="s">
-        <v>10</v>
+      <c r="E5" t="b">
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" t="b">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>450</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="A6" t="s">
         <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>500</v>
       </c>
       <c r="D6">
         <v>5.5</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="F6">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="b">
-        <v>0</v>
-      </c>
-      <c r="B7">
-        <v>700</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
+      <c r="C7">
+        <v>600</v>
       </c>
       <c r="D7">
         <v>6.5</v>
       </c>
-      <c r="E7" t="s">
-        <v>13</v>
+      <c r="E7" t="b">
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
